--- a/database/raw/dim_week.xlsx
+++ b/database/raw/dim_week.xlsx
@@ -7,21 +7,518 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="dim_week" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dim_week!$A$1:$I$157</definedName>
-  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+  <si>
+    <t>week_id</t>
+  </si>
+  <si>
+    <t>week_start_date</t>
+  </si>
+  <si>
+    <t>week_end_date</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>week_number</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>quarter</t>
+  </si>
+  <si>
+    <t>week_index</t>
+  </si>
+  <si>
+    <t>is_forecast</t>
+  </si>
+  <si>
+    <t>2024-W13</t>
+  </si>
+  <si>
+    <t>2024-W14</t>
+  </si>
+  <si>
+    <t>2024-W15</t>
+  </si>
+  <si>
+    <t>2024-W16</t>
+  </si>
+  <si>
+    <t>2024-W17</t>
+  </si>
+  <si>
+    <t>2024-W18</t>
+  </si>
+  <si>
+    <t>2024-W19</t>
+  </si>
+  <si>
+    <t>2024-W20</t>
+  </si>
+  <si>
+    <t>2024-W21</t>
+  </si>
+  <si>
+    <t>2024-W22</t>
+  </si>
+  <si>
+    <t>2024-W23</t>
+  </si>
+  <si>
+    <t>2024-W24</t>
+  </si>
+  <si>
+    <t>2024-W25</t>
+  </si>
+  <si>
+    <t>2024-W26</t>
+  </si>
+  <si>
+    <t>2024-W27</t>
+  </si>
+  <si>
+    <t>2024-W28</t>
+  </si>
+  <si>
+    <t>2024-W29</t>
+  </si>
+  <si>
+    <t>2024-W30</t>
+  </si>
+  <si>
+    <t>2024-W31</t>
+  </si>
+  <si>
+    <t>2024-W32</t>
+  </si>
+  <si>
+    <t>2024-W33</t>
+  </si>
+  <si>
+    <t>2024-W34</t>
+  </si>
+  <si>
+    <t>2024-W35</t>
+  </si>
+  <si>
+    <t>2024-W36</t>
+  </si>
+  <si>
+    <t>2024-W37</t>
+  </si>
+  <si>
+    <t>2024-W38</t>
+  </si>
+  <si>
+    <t>2024-W39</t>
+  </si>
+  <si>
+    <t>2024-W40</t>
+  </si>
+  <si>
+    <t>2024-W41</t>
+  </si>
+  <si>
+    <t>2024-W42</t>
+  </si>
+  <si>
+    <t>2024-W43</t>
+  </si>
+  <si>
+    <t>2024-W44</t>
+  </si>
+  <si>
+    <t>2024-W45</t>
+  </si>
+  <si>
+    <t>2024-W46</t>
+  </si>
+  <si>
+    <t>2024-W47</t>
+  </si>
+  <si>
+    <t>2024-W48</t>
+  </si>
+  <si>
+    <t>2024-W49</t>
+  </si>
+  <si>
+    <t>2024-W50</t>
+  </si>
+  <si>
+    <t>2024-W51</t>
+  </si>
+  <si>
+    <t>2024-W52</t>
+  </si>
+  <si>
+    <t>2025-W01</t>
+  </si>
+  <si>
+    <t>2025-W02</t>
+  </si>
+  <si>
+    <t>2025-W03</t>
+  </si>
+  <si>
+    <t>2025-W04</t>
+  </si>
+  <si>
+    <t>2025-W05</t>
+  </si>
+  <si>
+    <t>2025-W06</t>
+  </si>
+  <si>
+    <t>2025-W07</t>
+  </si>
+  <si>
+    <t>2025-W08</t>
+  </si>
+  <si>
+    <t>2025-W09</t>
+  </si>
+  <si>
+    <t>2025-W10</t>
+  </si>
+  <si>
+    <t>2025-W11</t>
+  </si>
+  <si>
+    <t>2025-W12</t>
+  </si>
+  <si>
+    <t>2025-W13</t>
+  </si>
+  <si>
+    <t>2025-W14</t>
+  </si>
+  <si>
+    <t>2025-W15</t>
+  </si>
+  <si>
+    <t>2025-W16</t>
+  </si>
+  <si>
+    <t>2025-W17</t>
+  </si>
+  <si>
+    <t>2025-W18</t>
+  </si>
+  <si>
+    <t>2025-W19</t>
+  </si>
+  <si>
+    <t>2025-W20</t>
+  </si>
+  <si>
+    <t>2025-W21</t>
+  </si>
+  <si>
+    <t>2025-W22</t>
+  </si>
+  <si>
+    <t>2025-W23</t>
+  </si>
+  <si>
+    <t>2025-W24</t>
+  </si>
+  <si>
+    <t>2025-W25</t>
+  </si>
+  <si>
+    <t>2025-W26</t>
+  </si>
+  <si>
+    <t>2025-W27</t>
+  </si>
+  <si>
+    <t>2025-W28</t>
+  </si>
+  <si>
+    <t>2025-W29</t>
+  </si>
+  <si>
+    <t>2025-W30</t>
+  </si>
+  <si>
+    <t>2025-W31</t>
+  </si>
+  <si>
+    <t>2025-W32</t>
+  </si>
+  <si>
+    <t>2025-W33</t>
+  </si>
+  <si>
+    <t>2025-W34</t>
+  </si>
+  <si>
+    <t>2025-W35</t>
+  </si>
+  <si>
+    <t>2025-W36</t>
+  </si>
+  <si>
+    <t>2025-W37</t>
+  </si>
+  <si>
+    <t>2025-W38</t>
+  </si>
+  <si>
+    <t>2025-W39</t>
+  </si>
+  <si>
+    <t>2025-W40</t>
+  </si>
+  <si>
+    <t>2025-W41</t>
+  </si>
+  <si>
+    <t>2025-W42</t>
+  </si>
+  <si>
+    <t>2025-W43</t>
+  </si>
+  <si>
+    <t>2025-W44</t>
+  </si>
+  <si>
+    <t>2025-W45</t>
+  </si>
+  <si>
+    <t>2025-W46</t>
+  </si>
+  <si>
+    <t>2025-W47</t>
+  </si>
+  <si>
+    <t>2025-W48</t>
+  </si>
+  <si>
+    <t>2025-W49</t>
+  </si>
+  <si>
+    <t>2025-W50</t>
+  </si>
+  <si>
+    <t>2025-W51</t>
+  </si>
+  <si>
+    <t>2025-W52</t>
+  </si>
+  <si>
+    <t>2026-W01</t>
+  </si>
+  <si>
+    <t>2026-W02</t>
+  </si>
+  <si>
+    <t>2026-W03</t>
+  </si>
+  <si>
+    <t>2026-W04</t>
+  </si>
+  <si>
+    <t>2026-W05</t>
+  </si>
+  <si>
+    <t>2026-W06</t>
+  </si>
+  <si>
+    <t>2026-W07</t>
+  </si>
+  <si>
+    <t>2026-W08</t>
+  </si>
+  <si>
+    <t>2026-W09</t>
+  </si>
+  <si>
+    <t>2026-W10</t>
+  </si>
+  <si>
+    <t>2026-W11</t>
+  </si>
+  <si>
+    <t>2026-W12</t>
+  </si>
+  <si>
+    <t>2026-W13</t>
+  </si>
+  <si>
+    <t>2026-W14</t>
+  </si>
+  <si>
+    <t>2026-W15</t>
+  </si>
+  <si>
+    <t>2026-W16</t>
+  </si>
+  <si>
+    <t>2026-W17</t>
+  </si>
+  <si>
+    <t>2026-W18</t>
+  </si>
+  <si>
+    <t>2026-W19</t>
+  </si>
+  <si>
+    <t>2026-W20</t>
+  </si>
+  <si>
+    <t>2026-W21</t>
+  </si>
+  <si>
+    <t>2026-W22</t>
+  </si>
+  <si>
+    <t>2026-W23</t>
+  </si>
+  <si>
+    <t>2026-W24</t>
+  </si>
+  <si>
+    <t>2026-W25</t>
+  </si>
+  <si>
+    <t>2026-W26</t>
+  </si>
+  <si>
+    <t>2026-W27</t>
+  </si>
+  <si>
+    <t>2026-W28</t>
+  </si>
+  <si>
+    <t>2026-W29</t>
+  </si>
+  <si>
+    <t>2026-W30</t>
+  </si>
+  <si>
+    <t>2026-W31</t>
+  </si>
+  <si>
+    <t>2026-W32</t>
+  </si>
+  <si>
+    <t>2026-W33</t>
+  </si>
+  <si>
+    <t>2026-W34</t>
+  </si>
+  <si>
+    <t>2026-W35</t>
+  </si>
+  <si>
+    <t>2026-W36</t>
+  </si>
+  <si>
+    <t>2026-W37</t>
+  </si>
+  <si>
+    <t>2026-W38</t>
+  </si>
+  <si>
+    <t>2026-W39</t>
+  </si>
+  <si>
+    <t>2026-W40</t>
+  </si>
+  <si>
+    <t>2026-W41</t>
+  </si>
+  <si>
+    <t>2026-W42</t>
+  </si>
+  <si>
+    <t>2026-W43</t>
+  </si>
+  <si>
+    <t>2026-W44</t>
+  </si>
+  <si>
+    <t>2026-W45</t>
+  </si>
+  <si>
+    <t>2026-W46</t>
+  </si>
+  <si>
+    <t>2026-W47</t>
+  </si>
+  <si>
+    <t>2026-W48</t>
+  </si>
+  <si>
+    <t>2026-W49</t>
+  </si>
+  <si>
+    <t>2026-W50</t>
+  </si>
+  <si>
+    <t>2026-W51</t>
+  </si>
+  <si>
+    <t>2026-W52</t>
+  </si>
+  <si>
+    <t>2026-W53</t>
+  </si>
+  <si>
+    <t>2027-W01</t>
+  </si>
+  <si>
+    <t>2027-W02</t>
+  </si>
+  <si>
+    <t>2027-W03</t>
+  </si>
+  <si>
+    <t>2027-W04</t>
+  </si>
+  <si>
+    <t>2027-W05</t>
+  </si>
+  <si>
+    <t>2027-W06</t>
+  </si>
+  <si>
+    <t>2027-W07</t>
+  </si>
+  <si>
+    <t>2027-W08</t>
+  </si>
+  <si>
+    <t>2027-W09</t>
+  </si>
+  <si>
+    <t>2027-W10</t>
+  </si>
+  <si>
+    <t>2027-W11</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -29,27 +526,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,11 +547,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -366,83 +846,54 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I157"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>week_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>week_start_date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>week_end_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>week_number</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>quarter</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>week_index</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>is_forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-W02</t>
-        </is>
-      </c>
-      <c r="B2" s="2">
-        <v>45663</v>
-      </c>
-      <c r="C2" s="2">
-        <v>45669</v>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1">
+        <v>45376</v>
+      </c>
+      <c r="C2" s="1">
+        <v>45382</v>
       </c>
       <c r="D2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -454,29 +905,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-W03</t>
-        </is>
-      </c>
-      <c r="B3" s="2">
-        <v>45670</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45676</v>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>45383</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45389</v>
       </c>
       <c r="D3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -485,29 +934,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-W04</t>
-        </is>
-      </c>
-      <c r="B4" s="2">
-        <v>45677</v>
-      </c>
-      <c r="C4" s="2">
-        <v>45683</v>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
+        <v>45390</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45396</v>
       </c>
       <c r="D4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -516,29 +963,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-W05</t>
-        </is>
-      </c>
-      <c r="B5" s="2">
-        <v>45684</v>
-      </c>
-      <c r="C5" s="2">
-        <v>45690</v>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1">
+        <v>45397</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45403</v>
       </c>
       <c r="D5">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -547,29 +992,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-W06</t>
-        </is>
-      </c>
-      <c r="B6" s="2">
-        <v>45691</v>
-      </c>
-      <c r="C6" s="2">
-        <v>45697</v>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1">
+        <v>45404</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45410</v>
       </c>
       <c r="D6">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -578,29 +1021,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-W07</t>
-        </is>
-      </c>
-      <c r="B7" s="2">
-        <v>45698</v>
-      </c>
-      <c r="C7" s="2">
-        <v>45704</v>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1">
+        <v>45411</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45417</v>
       </c>
       <c r="D7">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -609,29 +1050,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025-W08</t>
-        </is>
-      </c>
-      <c r="B8" s="2">
-        <v>45705</v>
-      </c>
-      <c r="C8" s="2">
-        <v>45711</v>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1">
+        <v>45418</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45424</v>
       </c>
       <c r="D8">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -640,29 +1079,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-W09</t>
-        </is>
-      </c>
-      <c r="B9" s="2">
-        <v>45712</v>
-      </c>
-      <c r="C9" s="2">
-        <v>45718</v>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1">
+        <v>45425</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45431</v>
       </c>
       <c r="D9">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E9">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -671,29 +1108,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025-W10</t>
-        </is>
-      </c>
-      <c r="B10" s="2">
-        <v>45719</v>
-      </c>
-      <c r="C10" s="2">
-        <v>45725</v>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1">
+        <v>45432</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45438</v>
       </c>
       <c r="D10">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>8</v>
@@ -702,29 +1137,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2025-W11</t>
-        </is>
-      </c>
-      <c r="B11" s="2">
-        <v>45726</v>
-      </c>
-      <c r="C11" s="2">
-        <v>45732</v>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1">
+        <v>45439</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45445</v>
       </c>
       <c r="D11">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -733,29 +1166,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-W12</t>
-        </is>
-      </c>
-      <c r="B12" s="2">
-        <v>45733</v>
-      </c>
-      <c r="C12" s="2">
-        <v>45739</v>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1">
+        <v>45446</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45452</v>
       </c>
       <c r="D12">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -764,29 +1195,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2025-W13</t>
-        </is>
-      </c>
-      <c r="B13" s="2">
-        <v>45740</v>
-      </c>
-      <c r="C13" s="2">
-        <v>45746</v>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45453</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45459</v>
       </c>
       <c r="D13">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>11</v>
@@ -795,29 +1224,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2025-W14</t>
-        </is>
-      </c>
-      <c r="B14" s="2">
-        <v>45747</v>
-      </c>
-      <c r="C14" s="2">
-        <v>45753</v>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1">
+        <v>45460</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45466</v>
       </c>
       <c r="D14">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>12</v>
@@ -826,26 +1253,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025-W15</t>
-        </is>
-      </c>
-      <c r="B15" s="2">
-        <v>45754</v>
-      </c>
-      <c r="C15" s="2">
-        <v>45760</v>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1">
+        <v>45467</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45473</v>
       </c>
       <c r="D15">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -857,29 +1282,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025-W16</t>
-        </is>
-      </c>
-      <c r="B16" s="2">
-        <v>45761</v>
-      </c>
-      <c r="C16" s="2">
-        <v>45767</v>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1">
+        <v>45474</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45480</v>
       </c>
       <c r="D16">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16">
         <v>14</v>
@@ -888,29 +1311,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-W17</t>
-        </is>
-      </c>
-      <c r="B17" s="2">
-        <v>45768</v>
-      </c>
-      <c r="C17" s="2">
-        <v>45774</v>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1">
+        <v>45481</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45487</v>
       </c>
       <c r="D17">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E17">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17">
         <v>15</v>
@@ -919,29 +1340,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-W18</t>
-        </is>
-      </c>
-      <c r="B18" s="2">
-        <v>45775</v>
-      </c>
-      <c r="C18" s="2">
-        <v>45781</v>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1">
+        <v>45488</v>
+      </c>
+      <c r="C18" s="1">
+        <v>45494</v>
       </c>
       <c r="D18">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>16</v>
@@ -950,29 +1369,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2025-W19</t>
-        </is>
-      </c>
-      <c r="B19" s="2">
-        <v>45782</v>
-      </c>
-      <c r="C19" s="2">
-        <v>45788</v>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1">
+        <v>45495</v>
+      </c>
+      <c r="C19" s="1">
+        <v>45501</v>
       </c>
       <c r="D19">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E19">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19">
         <v>17</v>
@@ -981,29 +1398,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2025-W20</t>
-        </is>
-      </c>
-      <c r="B20" s="2">
-        <v>45789</v>
-      </c>
-      <c r="C20" s="2">
-        <v>45795</v>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1">
+        <v>45502</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45508</v>
       </c>
       <c r="D20">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <v>18</v>
@@ -1012,29 +1427,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2025-W21</t>
-        </is>
-      </c>
-      <c r="B21" s="2">
-        <v>45796</v>
-      </c>
-      <c r="C21" s="2">
-        <v>45802</v>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1">
+        <v>45509</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45515</v>
       </c>
       <c r="D21">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <v>19</v>
@@ -1043,29 +1456,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2025-W22</t>
-        </is>
-      </c>
-      <c r="B22" s="2">
-        <v>45803</v>
-      </c>
-      <c r="C22" s="2">
-        <v>45809</v>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1">
+        <v>45516</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45522</v>
       </c>
       <c r="D22">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E22">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <v>20</v>
@@ -1074,29 +1485,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2025-W23</t>
-        </is>
-      </c>
-      <c r="B23" s="2">
-        <v>45810</v>
-      </c>
-      <c r="C23" s="2">
-        <v>45816</v>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1">
+        <v>45523</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45529</v>
       </c>
       <c r="D23">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23">
         <v>21</v>
@@ -1105,29 +1514,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-W24</t>
-        </is>
-      </c>
-      <c r="B24" s="2">
-        <v>45817</v>
-      </c>
-      <c r="C24" s="2">
-        <v>45823</v>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1">
+        <v>45530</v>
+      </c>
+      <c r="C24" s="1">
+        <v>45536</v>
       </c>
       <c r="D24">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E24">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>22</v>
@@ -1136,29 +1543,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-W25</t>
-        </is>
-      </c>
-      <c r="B25" s="2">
-        <v>45824</v>
-      </c>
-      <c r="C25" s="2">
-        <v>45830</v>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1">
+        <v>45537</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45543</v>
       </c>
       <c r="D25">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <v>23</v>
@@ -1167,29 +1572,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2025-W26</t>
-        </is>
-      </c>
-      <c r="B26" s="2">
-        <v>45831</v>
-      </c>
-      <c r="C26" s="2">
-        <v>45837</v>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1">
+        <v>45544</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45550</v>
       </c>
       <c r="D26">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E26">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26">
         <v>24</v>
@@ -1198,29 +1601,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2025-W27</t>
-        </is>
-      </c>
-      <c r="B27" s="2">
-        <v>45838</v>
-      </c>
-      <c r="C27" s="2">
-        <v>45844</v>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1">
+        <v>45551</v>
+      </c>
+      <c r="C27" s="1">
+        <v>45557</v>
       </c>
       <c r="D27">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E27">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27">
         <v>25</v>
@@ -1229,26 +1630,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-W28</t>
-        </is>
-      </c>
-      <c r="B28" s="2">
-        <v>45845</v>
-      </c>
-      <c r="C28" s="2">
-        <v>45851</v>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1">
+        <v>45558</v>
+      </c>
+      <c r="C28" s="1">
+        <v>45564</v>
       </c>
       <c r="D28">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E28">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28">
         <v>3</v>
@@ -1260,26 +1659,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-W29</t>
-        </is>
-      </c>
-      <c r="B29" s="2">
-        <v>45852</v>
-      </c>
-      <c r="C29" s="2">
-        <v>45858</v>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1">
+        <v>45565</v>
+      </c>
+      <c r="C29" s="1">
+        <v>45571</v>
       </c>
       <c r="D29">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E29">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G29">
         <v>3</v>
@@ -1291,29 +1688,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-W30</t>
-        </is>
-      </c>
-      <c r="B30" s="2">
-        <v>45859</v>
-      </c>
-      <c r="C30" s="2">
-        <v>45865</v>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1">
+        <v>45572</v>
+      </c>
+      <c r="C30" s="1">
+        <v>45578</v>
       </c>
       <c r="D30">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E30">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30">
         <v>28</v>
@@ -1322,29 +1717,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-W31</t>
-        </is>
-      </c>
-      <c r="B31" s="2">
-        <v>45866</v>
-      </c>
-      <c r="C31" s="2">
-        <v>45872</v>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1">
+        <v>45579</v>
+      </c>
+      <c r="C31" s="1">
+        <v>45585</v>
       </c>
       <c r="D31">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E31">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31">
         <v>29</v>
@@ -1353,29 +1746,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-W32</t>
-        </is>
-      </c>
-      <c r="B32" s="2">
-        <v>45873</v>
-      </c>
-      <c r="C32" s="2">
-        <v>45879</v>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1">
+        <v>45586</v>
+      </c>
+      <c r="C32" s="1">
+        <v>45592</v>
       </c>
       <c r="D32">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E32">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H32">
         <v>30</v>
@@ -1384,29 +1775,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-W33</t>
-        </is>
-      </c>
-      <c r="B33" s="2">
-        <v>45880</v>
-      </c>
-      <c r="C33" s="2">
-        <v>45886</v>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1">
+        <v>45593</v>
+      </c>
+      <c r="C33" s="1">
+        <v>45599</v>
       </c>
       <c r="D33">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E33">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33">
         <v>31</v>
@@ -1415,29 +1804,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2025-W34</t>
-        </is>
-      </c>
-      <c r="B34" s="2">
-        <v>45887</v>
-      </c>
-      <c r="C34" s="2">
-        <v>45893</v>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1">
+        <v>45600</v>
+      </c>
+      <c r="C34" s="1">
+        <v>45606</v>
       </c>
       <c r="D34">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E34">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34">
         <v>32</v>
@@ -1446,29 +1833,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2025-W35</t>
-        </is>
-      </c>
-      <c r="B35" s="2">
-        <v>45894</v>
-      </c>
-      <c r="C35" s="2">
-        <v>45900</v>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1">
+        <v>45607</v>
+      </c>
+      <c r="C35" s="1">
+        <v>45613</v>
       </c>
       <c r="D35">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E35">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35">
         <v>33</v>
@@ -1477,29 +1862,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2025-W36</t>
-        </is>
-      </c>
-      <c r="B36" s="2">
-        <v>45901</v>
-      </c>
-      <c r="C36" s="2">
-        <v>45907</v>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1">
+        <v>45614</v>
+      </c>
+      <c r="C36" s="1">
+        <v>45620</v>
       </c>
       <c r="D36">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E36">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36">
         <v>34</v>
@@ -1508,29 +1891,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2025-W37</t>
-        </is>
-      </c>
-      <c r="B37" s="2">
-        <v>45908</v>
-      </c>
-      <c r="C37" s="2">
-        <v>45914</v>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1">
+        <v>45621</v>
+      </c>
+      <c r="C37" s="1">
+        <v>45627</v>
       </c>
       <c r="D37">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E37">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37">
         <v>35</v>
@@ -1539,29 +1920,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2025-W38</t>
-        </is>
-      </c>
-      <c r="B38" s="2">
-        <v>45915</v>
-      </c>
-      <c r="C38" s="2">
-        <v>45921</v>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1">
+        <v>45628</v>
+      </c>
+      <c r="C38" s="1">
+        <v>45634</v>
       </c>
       <c r="D38">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E38">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F38">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>36</v>
@@ -1570,29 +1949,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2025-W39</t>
-        </is>
-      </c>
-      <c r="B39" s="2">
-        <v>45922</v>
-      </c>
-      <c r="C39" s="2">
-        <v>45928</v>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1">
+        <v>45635</v>
+      </c>
+      <c r="C39" s="1">
+        <v>45641</v>
       </c>
       <c r="D39">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E39">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F39">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39">
         <v>37</v>
@@ -1601,29 +1978,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2025-W40</t>
-        </is>
-      </c>
-      <c r="B40" s="2">
-        <v>45929</v>
-      </c>
-      <c r="C40" s="2">
-        <v>45935</v>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1">
+        <v>45642</v>
+      </c>
+      <c r="C40" s="1">
+        <v>45648</v>
       </c>
       <c r="D40">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E40">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F40">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H40">
         <v>38</v>
@@ -1632,26 +2007,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2025-W41</t>
-        </is>
-      </c>
-      <c r="B41" s="2">
-        <v>45936</v>
-      </c>
-      <c r="C41" s="2">
-        <v>45942</v>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1">
+        <v>45649</v>
+      </c>
+      <c r="C41" s="1">
+        <v>45655</v>
       </c>
       <c r="D41">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E41">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -1663,26 +2036,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2025-W42</t>
-        </is>
-      </c>
-      <c r="B42" s="2">
-        <v>45943</v>
-      </c>
-      <c r="C42" s="2">
-        <v>45949</v>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1">
+        <v>45656</v>
+      </c>
+      <c r="C42" s="1">
+        <v>45662</v>
       </c>
       <c r="D42">
         <v>2025</v>
       </c>
       <c r="E42">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -1694,29 +2065,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2025-W43</t>
-        </is>
-      </c>
-      <c r="B43" s="2">
-        <v>45950</v>
-      </c>
-      <c r="C43" s="2">
-        <v>45956</v>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1">
+        <v>45663</v>
+      </c>
+      <c r="C43" s="1">
+        <v>45669</v>
       </c>
       <c r="D43">
         <v>2025</v>
       </c>
       <c r="E43">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>41</v>
@@ -1725,29 +2094,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2025-W44</t>
-        </is>
-      </c>
-      <c r="B44" s="2">
-        <v>45957</v>
-      </c>
-      <c r="C44" s="2">
-        <v>45963</v>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1">
+        <v>45670</v>
+      </c>
+      <c r="C44" s="1">
+        <v>45676</v>
       </c>
       <c r="D44">
         <v>2025</v>
       </c>
       <c r="E44">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>42</v>
@@ -1756,29 +2123,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2025-W45</t>
-        </is>
-      </c>
-      <c r="B45" s="2">
-        <v>45964</v>
-      </c>
-      <c r="C45" s="2">
-        <v>45970</v>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1">
+        <v>45677</v>
+      </c>
+      <c r="C45" s="1">
+        <v>45683</v>
       </c>
       <c r="D45">
         <v>2025</v>
       </c>
       <c r="E45">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>43</v>
@@ -1787,29 +2152,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2025-W46</t>
-        </is>
-      </c>
-      <c r="B46" s="2">
-        <v>45971</v>
-      </c>
-      <c r="C46" s="2">
-        <v>45977</v>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1">
+        <v>45684</v>
+      </c>
+      <c r="C46" s="1">
+        <v>45690</v>
       </c>
       <c r="D46">
         <v>2025</v>
       </c>
       <c r="E46">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="F46">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>44</v>
@@ -1818,29 +2181,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2025-W47</t>
-        </is>
-      </c>
-      <c r="B47" s="2">
-        <v>45978</v>
-      </c>
-      <c r="C47" s="2">
-        <v>45984</v>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1">
+        <v>45691</v>
+      </c>
+      <c r="C47" s="1">
+        <v>45697</v>
       </c>
       <c r="D47">
         <v>2025</v>
       </c>
       <c r="E47">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F47">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H47">
         <v>45</v>
@@ -1849,29 +2210,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2025-W48</t>
-        </is>
-      </c>
-      <c r="B48" s="2">
-        <v>45985</v>
-      </c>
-      <c r="C48" s="2">
-        <v>45991</v>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1">
+        <v>45698</v>
+      </c>
+      <c r="C48" s="1">
+        <v>45704</v>
       </c>
       <c r="D48">
         <v>2025</v>
       </c>
       <c r="E48">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="F48">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>46</v>
@@ -1880,29 +2239,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2025-W49</t>
-        </is>
-      </c>
-      <c r="B49" s="2">
-        <v>45992</v>
-      </c>
-      <c r="C49" s="2">
-        <v>45998</v>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1">
+        <v>45705</v>
+      </c>
+      <c r="C49" s="1">
+        <v>45711</v>
       </c>
       <c r="D49">
         <v>2025</v>
       </c>
       <c r="E49">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="F49">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H49">
         <v>47</v>
@@ -1911,29 +2268,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2025-W50</t>
-        </is>
-      </c>
-      <c r="B50" s="2">
-        <v>45999</v>
-      </c>
-      <c r="C50" s="2">
-        <v>46005</v>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1">
+        <v>45712</v>
+      </c>
+      <c r="C50" s="1">
+        <v>45718</v>
       </c>
       <c r="D50">
         <v>2025</v>
       </c>
       <c r="E50">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F50">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>48</v>
@@ -1942,29 +2297,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2025-W51</t>
-        </is>
-      </c>
-      <c r="B51" s="2">
-        <v>46006</v>
-      </c>
-      <c r="C51" s="2">
-        <v>46012</v>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1">
+        <v>45719</v>
+      </c>
+      <c r="C51" s="1">
+        <v>45725</v>
       </c>
       <c r="D51">
         <v>2025</v>
       </c>
       <c r="E51">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F51">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>49</v>
@@ -1973,29 +2326,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2025-W52</t>
-        </is>
-      </c>
-      <c r="B52" s="2">
-        <v>46013</v>
-      </c>
-      <c r="C52" s="2">
-        <v>46019</v>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1">
+        <v>45726</v>
+      </c>
+      <c r="C52" s="1">
+        <v>45732</v>
       </c>
       <c r="D52">
         <v>2025</v>
       </c>
       <c r="E52">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F52">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>50</v>
@@ -2004,29 +2355,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-W01</t>
-        </is>
-      </c>
-      <c r="B53" s="2">
-        <v>46020</v>
-      </c>
-      <c r="C53" s="2">
-        <v>46026</v>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1">
+        <v>45733</v>
+      </c>
+      <c r="C53" s="1">
+        <v>45739</v>
       </c>
       <c r="D53">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F53">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H53">
         <v>51</v>
@@ -2035,26 +2384,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-W02</t>
-        </is>
-      </c>
-      <c r="B54" s="2">
-        <v>46027</v>
-      </c>
-      <c r="C54" s="2">
-        <v>46033</v>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1">
+        <v>45740</v>
+      </c>
+      <c r="C54" s="1">
+        <v>45746</v>
       </c>
       <c r="D54">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2066,26 +2413,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-W03</t>
-        </is>
-      </c>
-      <c r="B55" s="2">
-        <v>46034</v>
-      </c>
-      <c r="C55" s="2">
-        <v>46040</v>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1">
+        <v>45747</v>
+      </c>
+      <c r="C55" s="1">
+        <v>45753</v>
       </c>
       <c r="D55">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2097,29 +2442,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-W04</t>
-        </is>
-      </c>
-      <c r="B56" s="2">
-        <v>46041</v>
-      </c>
-      <c r="C56" s="2">
-        <v>46047</v>
+    <row r="56" spans="1:9">
+      <c r="A56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1">
+        <v>45754</v>
+      </c>
+      <c r="C56" s="1">
+        <v>45760</v>
       </c>
       <c r="D56">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56">
         <v>54</v>
@@ -2128,29 +2471,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-W05</t>
-        </is>
-      </c>
-      <c r="B57" s="2">
-        <v>46048</v>
-      </c>
-      <c r="C57" s="2">
-        <v>46054</v>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1">
+        <v>45761</v>
+      </c>
+      <c r="C57" s="1">
+        <v>45767</v>
       </c>
       <c r="D57">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57">
         <v>55</v>
@@ -2159,29 +2500,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-W06</t>
-        </is>
-      </c>
-      <c r="B58" s="2">
-        <v>46055</v>
-      </c>
-      <c r="C58" s="2">
-        <v>46061</v>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1">
+        <v>45768</v>
+      </c>
+      <c r="C58" s="1">
+        <v>45774</v>
       </c>
       <c r="D58">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E58">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58">
         <v>56</v>
@@ -2190,29 +2529,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-W07</t>
-        </is>
-      </c>
-      <c r="B59" s="2">
-        <v>46062</v>
-      </c>
-      <c r="C59" s="2">
-        <v>46068</v>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1">
+        <v>45775</v>
+      </c>
+      <c r="C59" s="1">
+        <v>45781</v>
       </c>
       <c r="D59">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E59">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59">
         <v>57</v>
@@ -2221,29 +2558,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-W08</t>
-        </is>
-      </c>
-      <c r="B60" s="2">
-        <v>46069</v>
-      </c>
-      <c r="C60" s="2">
-        <v>46075</v>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1">
+        <v>45782</v>
+      </c>
+      <c r="C60" s="1">
+        <v>45788</v>
       </c>
       <c r="D60">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E60">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60">
         <v>58</v>
@@ -2252,29 +2587,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-W09</t>
-        </is>
-      </c>
-      <c r="B61" s="2">
-        <v>46076</v>
-      </c>
-      <c r="C61" s="2">
-        <v>46082</v>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1">
+        <v>45789</v>
+      </c>
+      <c r="C61" s="1">
+        <v>45795</v>
       </c>
       <c r="D61">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E61">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61">
         <v>59</v>
@@ -2283,29 +2616,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-W10</t>
-        </is>
-      </c>
-      <c r="B62" s="2">
-        <v>46083</v>
-      </c>
-      <c r="C62" s="2">
-        <v>46089</v>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1">
+        <v>45796</v>
+      </c>
+      <c r="C62" s="1">
+        <v>45802</v>
       </c>
       <c r="D62">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E62">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
         <v>60</v>
@@ -2314,29 +2645,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-W11</t>
-        </is>
-      </c>
-      <c r="B63" s="2">
-        <v>46090</v>
-      </c>
-      <c r="C63" s="2">
-        <v>46096</v>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1">
+        <v>45803</v>
+      </c>
+      <c r="C63" s="1">
+        <v>45809</v>
       </c>
       <c r="D63">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E63">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63">
         <v>61</v>
@@ -2345,29 +2674,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-W12</t>
-        </is>
-      </c>
-      <c r="B64" s="2">
-        <v>46097</v>
-      </c>
-      <c r="C64" s="2">
-        <v>46103</v>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1">
+        <v>45810</v>
+      </c>
+      <c r="C64" s="1">
+        <v>45816</v>
       </c>
       <c r="D64">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E64">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
         <v>62</v>
@@ -2376,29 +2703,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-W13</t>
-        </is>
-      </c>
-      <c r="B65" s="2">
-        <v>46104</v>
-      </c>
-      <c r="C65" s="2">
-        <v>46110</v>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1">
+        <v>45817</v>
+      </c>
+      <c r="C65" s="1">
+        <v>45823</v>
       </c>
       <c r="D65">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E65">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65">
         <v>63</v>
@@ -2407,29 +2732,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-W14</t>
-        </is>
-      </c>
-      <c r="B66" s="2">
-        <v>46111</v>
-      </c>
-      <c r="C66" s="2">
-        <v>46117</v>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1">
+        <v>45824</v>
+      </c>
+      <c r="C66" s="1">
+        <v>45830</v>
       </c>
       <c r="D66">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E66">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66">
         <v>64</v>
@@ -2438,26 +2761,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-W15</t>
-        </is>
-      </c>
-      <c r="B67" s="2">
-        <v>46118</v>
-      </c>
-      <c r="C67" s="2">
-        <v>46124</v>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1">
+        <v>45831</v>
+      </c>
+      <c r="C67" s="1">
+        <v>45837</v>
       </c>
       <c r="D67">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E67">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G67">
         <v>2</v>
@@ -2469,26 +2790,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="B68" s="2">
-        <v>46125</v>
-      </c>
-      <c r="C68" s="2">
-        <v>46131</v>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="1">
+        <v>45838</v>
+      </c>
+      <c r="C68" s="1">
+        <v>45844</v>
       </c>
       <c r="D68">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E68">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G68">
         <v>2</v>
@@ -2500,29 +2819,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-W17</t>
-        </is>
-      </c>
-      <c r="B69" s="2">
-        <v>46132</v>
-      </c>
-      <c r="C69" s="2">
-        <v>46138</v>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="1">
+        <v>45845</v>
+      </c>
+      <c r="C69" s="1">
+        <v>45851</v>
       </c>
       <c r="D69">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E69">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69">
         <v>67</v>
@@ -2531,29 +2848,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-W18</t>
-        </is>
-      </c>
-      <c r="B70" s="2">
-        <v>46139</v>
-      </c>
-      <c r="C70" s="2">
-        <v>46145</v>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="1">
+        <v>45852</v>
+      </c>
+      <c r="C70" s="1">
+        <v>45858</v>
       </c>
       <c r="D70">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E70">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H70">
         <v>68</v>
@@ -2562,29 +2877,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-W19</t>
-        </is>
-      </c>
-      <c r="B71" s="2">
-        <v>46146</v>
-      </c>
-      <c r="C71" s="2">
-        <v>46152</v>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="1">
+        <v>45859</v>
+      </c>
+      <c r="C71" s="1">
+        <v>45865</v>
       </c>
       <c r="D71">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E71">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71">
         <v>69</v>
@@ -2593,29 +2906,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-W20</t>
-        </is>
-      </c>
-      <c r="B72" s="2">
-        <v>46153</v>
-      </c>
-      <c r="C72" s="2">
-        <v>46159</v>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1">
+        <v>45866</v>
+      </c>
+      <c r="C72" s="1">
+        <v>45872</v>
       </c>
       <c r="D72">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E72">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72">
         <v>70</v>
@@ -2624,29 +2935,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-W21</t>
-        </is>
-      </c>
-      <c r="B73" s="2">
-        <v>46160</v>
-      </c>
-      <c r="C73" s="2">
-        <v>46166</v>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="1">
+        <v>45873</v>
+      </c>
+      <c r="C73" s="1">
+        <v>45879</v>
       </c>
       <c r="D73">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E73">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F73">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H73">
         <v>71</v>
@@ -2655,29 +2964,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-W22</t>
-        </is>
-      </c>
-      <c r="B74" s="2">
-        <v>46167</v>
-      </c>
-      <c r="C74" s="2">
-        <v>46173</v>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1">
+        <v>45880</v>
+      </c>
+      <c r="C74" s="1">
+        <v>45886</v>
       </c>
       <c r="D74">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E74">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74">
         <v>72</v>
@@ -2686,29 +2993,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-W23</t>
-        </is>
-      </c>
-      <c r="B75" s="2">
-        <v>46174</v>
-      </c>
-      <c r="C75" s="2">
-        <v>46180</v>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="1">
+        <v>45887</v>
+      </c>
+      <c r="C75" s="1">
+        <v>45893</v>
       </c>
       <c r="D75">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E75">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F75">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75">
         <v>73</v>
@@ -2717,29 +3022,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-W24</t>
-        </is>
-      </c>
-      <c r="B76" s="2">
-        <v>46181</v>
-      </c>
-      <c r="C76" s="2">
-        <v>46187</v>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="1">
+        <v>45894</v>
+      </c>
+      <c r="C76" s="1">
+        <v>45900</v>
       </c>
       <c r="D76">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E76">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F76">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76">
         <v>74</v>
@@ -2748,29 +3051,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-W25</t>
-        </is>
-      </c>
-      <c r="B77" s="2">
-        <v>46188</v>
-      </c>
-      <c r="C77" s="2">
-        <v>46194</v>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="1">
+        <v>45901</v>
+      </c>
+      <c r="C77" s="1">
+        <v>45907</v>
       </c>
       <c r="D77">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E77">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F77">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H77">
         <v>75</v>
@@ -2779,29 +3080,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-W26</t>
-        </is>
-      </c>
-      <c r="B78" s="2">
-        <v>46195</v>
-      </c>
-      <c r="C78" s="2">
-        <v>46201</v>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="1">
+        <v>45908</v>
+      </c>
+      <c r="C78" s="1">
+        <v>45914</v>
       </c>
       <c r="D78">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E78">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F78">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78">
         <v>76</v>
@@ -2810,29 +3109,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-W27</t>
-        </is>
-      </c>
-      <c r="B79" s="2">
-        <v>46202</v>
-      </c>
-      <c r="C79" s="2">
-        <v>46208</v>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="1">
+        <v>45915</v>
+      </c>
+      <c r="C79" s="1">
+        <v>45921</v>
       </c>
       <c r="D79">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E79">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F79">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79">
         <v>77</v>
@@ -2841,26 +3138,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-W28</t>
-        </is>
-      </c>
-      <c r="B80" s="2">
-        <v>46209</v>
-      </c>
-      <c r="C80" s="2">
-        <v>46215</v>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="1">
+        <v>45922</v>
+      </c>
+      <c r="C80" s="1">
+        <v>45928</v>
       </c>
       <c r="D80">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E80">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F80">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G80">
         <v>3</v>
@@ -2872,26 +3167,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-W29</t>
-        </is>
-      </c>
-      <c r="B81" s="2">
-        <v>46216</v>
-      </c>
-      <c r="C81" s="2">
-        <v>46222</v>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="1">
+        <v>45929</v>
+      </c>
+      <c r="C81" s="1">
+        <v>45935</v>
       </c>
       <c r="D81">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E81">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F81">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G81">
         <v>3</v>
@@ -2903,29 +3196,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-W30</t>
-        </is>
-      </c>
-      <c r="B82" s="2">
-        <v>46223</v>
-      </c>
-      <c r="C82" s="2">
-        <v>46229</v>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="1">
+        <v>45936</v>
+      </c>
+      <c r="C82" s="1">
+        <v>45942</v>
       </c>
       <c r="D82">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E82">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F82">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H82">
         <v>80</v>
@@ -2934,29 +3225,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-W31</t>
-        </is>
-      </c>
-      <c r="B83" s="2">
-        <v>46230</v>
-      </c>
-      <c r="C83" s="2">
-        <v>46236</v>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="1">
+        <v>45943</v>
+      </c>
+      <c r="C83" s="1">
+        <v>45949</v>
       </c>
       <c r="D83">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E83">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F83">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H83">
         <v>81</v>
@@ -2965,29 +3254,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-W32</t>
-        </is>
-      </c>
-      <c r="B84" s="2">
-        <v>46237</v>
-      </c>
-      <c r="C84" s="2">
-        <v>46243</v>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="1">
+        <v>45950</v>
+      </c>
+      <c r="C84" s="1">
+        <v>45956</v>
       </c>
       <c r="D84">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E84">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F84">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H84">
         <v>82</v>
@@ -2996,29 +3283,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-W33</t>
-        </is>
-      </c>
-      <c r="B85" s="2">
-        <v>46244</v>
-      </c>
-      <c r="C85" s="2">
-        <v>46250</v>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="1">
+        <v>45957</v>
+      </c>
+      <c r="C85" s="1">
+        <v>45963</v>
       </c>
       <c r="D85">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E85">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F85">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H85">
         <v>83</v>
@@ -3027,29 +3312,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-W34</t>
-        </is>
-      </c>
-      <c r="B86" s="2">
-        <v>46251</v>
-      </c>
-      <c r="C86" s="2">
-        <v>46257</v>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="1">
+        <v>45964</v>
+      </c>
+      <c r="C86" s="1">
+        <v>45970</v>
       </c>
       <c r="D86">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E86">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F86">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H86">
         <v>84</v>
@@ -3058,29 +3341,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-W35</t>
-        </is>
-      </c>
-      <c r="B87" s="2">
-        <v>46258</v>
-      </c>
-      <c r="C87" s="2">
-        <v>46264</v>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="1">
+        <v>45971</v>
+      </c>
+      <c r="C87" s="1">
+        <v>45977</v>
       </c>
       <c r="D87">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E87">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F87">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H87">
         <v>85</v>
@@ -3089,29 +3370,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-W36</t>
-        </is>
-      </c>
-      <c r="B88" s="2">
-        <v>46265</v>
-      </c>
-      <c r="C88" s="2">
-        <v>46271</v>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="1">
+        <v>45978</v>
+      </c>
+      <c r="C88" s="1">
+        <v>45984</v>
       </c>
       <c r="D88">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E88">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F88">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H88">
         <v>86</v>
@@ -3120,29 +3399,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-W37</t>
-        </is>
-      </c>
-      <c r="B89" s="2">
-        <v>46272</v>
-      </c>
-      <c r="C89" s="2">
-        <v>46278</v>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="1">
+        <v>45985</v>
+      </c>
+      <c r="C89" s="1">
+        <v>45991</v>
       </c>
       <c r="D89">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E89">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F89">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H89">
         <v>87</v>
@@ -3151,29 +3428,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-W38</t>
-        </is>
-      </c>
-      <c r="B90" s="2">
-        <v>46279</v>
-      </c>
-      <c r="C90" s="2">
-        <v>46285</v>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="1">
+        <v>45992</v>
+      </c>
+      <c r="C90" s="1">
+        <v>45998</v>
       </c>
       <c r="D90">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E90">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F90">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H90">
         <v>88</v>
@@ -3182,29 +3457,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-W39</t>
-        </is>
-      </c>
-      <c r="B91" s="2">
-        <v>46286</v>
-      </c>
-      <c r="C91" s="2">
-        <v>46292</v>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="1">
+        <v>45999</v>
+      </c>
+      <c r="C91" s="1">
+        <v>46005</v>
       </c>
       <c r="D91">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E91">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F91">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H91">
         <v>89</v>
@@ -3213,29 +3486,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-W40</t>
-        </is>
-      </c>
-      <c r="B92" s="2">
-        <v>46293</v>
-      </c>
-      <c r="C92" s="2">
-        <v>46299</v>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46006</v>
+      </c>
+      <c r="C92" s="1">
+        <v>46012</v>
       </c>
       <c r="D92">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E92">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F92">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G92">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H92">
         <v>90</v>
@@ -3244,26 +3515,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-W41</t>
-        </is>
-      </c>
-      <c r="B93" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C93" s="2">
-        <v>46306</v>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46013</v>
+      </c>
+      <c r="C93" s="1">
+        <v>46019</v>
       </c>
       <c r="D93">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E93">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F93">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G93">
         <v>4</v>
@@ -3275,26 +3544,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-W42</t>
-        </is>
-      </c>
-      <c r="B94" s="2">
-        <v>46307</v>
-      </c>
-      <c r="C94" s="2">
-        <v>46313</v>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="1">
+        <v>46020</v>
+      </c>
+      <c r="C94" s="1">
+        <v>46026</v>
       </c>
       <c r="D94">
         <v>2026</v>
       </c>
       <c r="E94">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F94">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G94">
         <v>4</v>
@@ -3306,29 +3573,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-W43</t>
-        </is>
-      </c>
-      <c r="B95" s="2">
-        <v>46314</v>
-      </c>
-      <c r="C95" s="2">
-        <v>46320</v>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" s="1">
+        <v>46027</v>
+      </c>
+      <c r="C95" s="1">
+        <v>46033</v>
       </c>
       <c r="D95">
         <v>2026</v>
       </c>
       <c r="E95">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="F95">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G95">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H95">
         <v>93</v>
@@ -3337,29 +3602,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-W44</t>
-        </is>
-      </c>
-      <c r="B96" s="2">
-        <v>46321</v>
-      </c>
-      <c r="C96" s="2">
-        <v>46327</v>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="1">
+        <v>46034</v>
+      </c>
+      <c r="C96" s="1">
+        <v>46040</v>
       </c>
       <c r="D96">
         <v>2026</v>
       </c>
       <c r="E96">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="F96">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H96">
         <v>94</v>
@@ -3368,29 +3631,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-W45</t>
-        </is>
-      </c>
-      <c r="B97" s="2">
-        <v>46328</v>
-      </c>
-      <c r="C97" s="2">
-        <v>46334</v>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="1">
+        <v>46041</v>
+      </c>
+      <c r="C97" s="1">
+        <v>46047</v>
       </c>
       <c r="D97">
         <v>2026</v>
       </c>
       <c r="E97">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F97">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G97">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H97">
         <v>95</v>
@@ -3399,29 +3660,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-W46</t>
-        </is>
-      </c>
-      <c r="B98" s="2">
-        <v>46335</v>
-      </c>
-      <c r="C98" s="2">
-        <v>46341</v>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46048</v>
+      </c>
+      <c r="C98" s="1">
+        <v>46054</v>
       </c>
       <c r="D98">
         <v>2026</v>
       </c>
       <c r="E98">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="F98">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H98">
         <v>96</v>
@@ -3430,29 +3689,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-W47</t>
-        </is>
-      </c>
-      <c r="B99" s="2">
-        <v>46342</v>
-      </c>
-      <c r="C99" s="2">
-        <v>46348</v>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="1">
+        <v>46055</v>
+      </c>
+      <c r="C99" s="1">
+        <v>46061</v>
       </c>
       <c r="D99">
         <v>2026</v>
       </c>
       <c r="E99">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F99">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>97</v>
@@ -3461,29 +3718,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-W48</t>
-        </is>
-      </c>
-      <c r="B100" s="2">
-        <v>46349</v>
-      </c>
-      <c r="C100" s="2">
-        <v>46355</v>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="1">
+        <v>46062</v>
+      </c>
+      <c r="C100" s="1">
+        <v>46068</v>
       </c>
       <c r="D100">
         <v>2026</v>
       </c>
       <c r="E100">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="F100">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G100">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>98</v>
@@ -3492,29 +3747,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-W49</t>
-        </is>
-      </c>
-      <c r="B101" s="2">
-        <v>46356</v>
-      </c>
-      <c r="C101" s="2">
-        <v>46362</v>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" s="1">
+        <v>46069</v>
+      </c>
+      <c r="C101" s="1">
+        <v>46075</v>
       </c>
       <c r="D101">
         <v>2026</v>
       </c>
       <c r="E101">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="F101">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G101">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H101">
         <v>99</v>
@@ -3523,29 +3776,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-W50</t>
-        </is>
-      </c>
-      <c r="B102" s="2">
-        <v>46363</v>
-      </c>
-      <c r="C102" s="2">
-        <v>46369</v>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C102" s="1">
+        <v>46082</v>
       </c>
       <c r="D102">
         <v>2026</v>
       </c>
       <c r="E102">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F102">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G102">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H102">
         <v>100</v>
@@ -3554,29 +3805,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-W51</t>
-        </is>
-      </c>
-      <c r="B103" s="2">
-        <v>46370</v>
-      </c>
-      <c r="C103" s="2">
-        <v>46376</v>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C103" s="1">
+        <v>46089</v>
       </c>
       <c r="D103">
         <v>2026</v>
       </c>
       <c r="E103">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F103">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G103">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H103">
         <v>101</v>
@@ -3585,29 +3834,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-W52</t>
-        </is>
-      </c>
-      <c r="B104" s="2">
-        <v>46377</v>
-      </c>
-      <c r="C104" s="2">
-        <v>46383</v>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C104" s="1">
+        <v>46096</v>
       </c>
       <c r="D104">
         <v>2026</v>
       </c>
       <c r="E104">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F104">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G104">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H104">
         <v>102</v>
@@ -3616,29 +3863,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-W53</t>
-        </is>
-      </c>
-      <c r="B105" s="2">
-        <v>46384</v>
-      </c>
-      <c r="C105" s="2">
-        <v>46390</v>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C105" s="1">
+        <v>46103</v>
       </c>
       <c r="D105">
         <v>2026</v>
       </c>
       <c r="E105">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="F105">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G105">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H105">
         <v>103</v>
@@ -3647,26 +3892,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2027-W01</t>
-        </is>
-      </c>
-      <c r="B106" s="2">
-        <v>46391</v>
-      </c>
-      <c r="C106" s="2">
-        <v>46397</v>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" s="1">
+        <v>46104</v>
+      </c>
+      <c r="C106" s="1">
+        <v>46110</v>
       </c>
       <c r="D106">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E106">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G106">
         <v>1</v>
@@ -3678,26 +3921,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2027-W02</t>
-        </is>
-      </c>
-      <c r="B107" s="2">
-        <v>46398</v>
-      </c>
-      <c r="C107" s="2">
-        <v>46404</v>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>114</v>
+      </c>
+      <c r="B107" s="1">
+        <v>46111</v>
+      </c>
+      <c r="C107" s="1">
+        <v>46117</v>
       </c>
       <c r="D107">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E107">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -3709,29 +3950,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2027-W03</t>
-        </is>
-      </c>
-      <c r="B108" s="2">
-        <v>46405</v>
-      </c>
-      <c r="C108" s="2">
-        <v>46411</v>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" s="1">
+        <v>46118</v>
+      </c>
+      <c r="C108" s="1">
+        <v>46124</v>
       </c>
       <c r="D108">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E108">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108">
         <v>106</v>
@@ -3740,29 +3979,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2027-W04</t>
-        </is>
-      </c>
-      <c r="B109" s="2">
-        <v>46412</v>
-      </c>
-      <c r="C109" s="2">
-        <v>46418</v>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>116</v>
+      </c>
+      <c r="B109" s="1">
+        <v>46125</v>
+      </c>
+      <c r="C109" s="1">
+        <v>46131</v>
       </c>
       <c r="D109">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E109">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H109">
         <v>107</v>
@@ -3771,29 +4008,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2027-W05</t>
-        </is>
-      </c>
-      <c r="B110" s="2">
-        <v>46419</v>
-      </c>
-      <c r="C110" s="2">
-        <v>46425</v>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>117</v>
+      </c>
+      <c r="B110" s="1">
+        <v>46132</v>
+      </c>
+      <c r="C110" s="1">
+        <v>46138</v>
       </c>
       <c r="D110">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E110">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F110">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H110">
         <v>108</v>
@@ -3802,29 +4037,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2027-W06</t>
-        </is>
-      </c>
-      <c r="B111" s="2">
-        <v>46426</v>
-      </c>
-      <c r="C111" s="2">
-        <v>46432</v>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" s="1">
+        <v>46139</v>
+      </c>
+      <c r="C111" s="1">
+        <v>46145</v>
       </c>
       <c r="D111">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E111">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F111">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H111">
         <v>109</v>
@@ -3833,29 +4066,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2027-W07</t>
-        </is>
-      </c>
-      <c r="B112" s="2">
-        <v>46433</v>
-      </c>
-      <c r="C112" s="2">
-        <v>46439</v>
+    <row r="112" spans="1:9">
+      <c r="A112" t="s">
+        <v>119</v>
+      </c>
+      <c r="B112" s="1">
+        <v>46146</v>
+      </c>
+      <c r="C112" s="1">
+        <v>46152</v>
       </c>
       <c r="D112">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E112">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F112">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H112">
         <v>110</v>
@@ -3864,29 +4095,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2027-W08</t>
-        </is>
-      </c>
-      <c r="B113" s="2">
-        <v>46440</v>
-      </c>
-      <c r="C113" s="2">
-        <v>46446</v>
+    <row r="113" spans="1:9">
+      <c r="A113" t="s">
+        <v>120</v>
+      </c>
+      <c r="B113" s="1">
+        <v>46153</v>
+      </c>
+      <c r="C113" s="1">
+        <v>46159</v>
       </c>
       <c r="D113">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E113">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F113">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113">
         <v>111</v>
@@ -3895,29 +4124,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2027-W09</t>
-        </is>
-      </c>
-      <c r="B114" s="2">
-        <v>46447</v>
-      </c>
-      <c r="C114" s="2">
-        <v>46453</v>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" s="1">
+        <v>46160</v>
+      </c>
+      <c r="C114" s="1">
+        <v>46166</v>
       </c>
       <c r="D114">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E114">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F114">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114">
         <v>112</v>
@@ -3926,29 +4153,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2027-W10</t>
-        </is>
-      </c>
-      <c r="B115" s="2">
-        <v>46454</v>
-      </c>
-      <c r="C115" s="2">
-        <v>46460</v>
+    <row r="115" spans="1:9">
+      <c r="A115" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" s="1">
+        <v>46167</v>
+      </c>
+      <c r="C115" s="1">
+        <v>46173</v>
       </c>
       <c r="D115">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E115">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F115">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H115">
         <v>113</v>
@@ -3957,29 +4182,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2027-W11</t>
-        </is>
-      </c>
-      <c r="B116" s="2">
-        <v>46461</v>
-      </c>
-      <c r="C116" s="2">
-        <v>46467</v>
+    <row r="116" spans="1:9">
+      <c r="A116" t="s">
+        <v>123</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C116" s="1">
+        <v>46180</v>
       </c>
       <c r="D116">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E116">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F116">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116">
         <v>114</v>
@@ -3988,29 +4211,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2027-W12</t>
-        </is>
-      </c>
-      <c r="B117" s="2">
-        <v>46468</v>
-      </c>
-      <c r="C117" s="2">
-        <v>46474</v>
+    <row r="117" spans="1:9">
+      <c r="A117" t="s">
+        <v>124</v>
+      </c>
+      <c r="B117" s="1">
+        <v>46181</v>
+      </c>
+      <c r="C117" s="1">
+        <v>46187</v>
       </c>
       <c r="D117">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E117">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F117">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H117">
         <v>115</v>
@@ -4019,29 +4240,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2027-W13</t>
-        </is>
-      </c>
-      <c r="B118" s="2">
-        <v>46475</v>
-      </c>
-      <c r="C118" s="2">
-        <v>46481</v>
+    <row r="118" spans="1:9">
+      <c r="A118" t="s">
+        <v>125</v>
+      </c>
+      <c r="B118" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C118" s="1">
+        <v>46194</v>
       </c>
       <c r="D118">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E118">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F118">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118">
         <v>116</v>
@@ -4050,26 +4269,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2027-W14</t>
-        </is>
-      </c>
-      <c r="B119" s="2">
-        <v>46482</v>
-      </c>
-      <c r="C119" s="2">
-        <v>46488</v>
+    <row r="119" spans="1:9">
+      <c r="A119" t="s">
+        <v>126</v>
+      </c>
+      <c r="B119" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C119" s="1">
+        <v>46201</v>
       </c>
       <c r="D119">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E119">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F119">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G119">
         <v>2</v>
@@ -4081,26 +4298,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2027-W15</t>
-        </is>
-      </c>
-      <c r="B120" s="2">
-        <v>46489</v>
-      </c>
-      <c r="C120" s="2">
-        <v>46495</v>
+    <row r="120" spans="1:9">
+      <c r="A120" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" s="1">
+        <v>46202</v>
+      </c>
+      <c r="C120" s="1">
+        <v>46208</v>
       </c>
       <c r="D120">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E120">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F120">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G120">
         <v>2</v>
@@ -4112,29 +4327,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2027-W16</t>
-        </is>
-      </c>
-      <c r="B121" s="2">
-        <v>46496</v>
-      </c>
-      <c r="C121" s="2">
-        <v>46502</v>
+    <row r="121" spans="1:9">
+      <c r="A121" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" s="1">
+        <v>46209</v>
+      </c>
+      <c r="C121" s="1">
+        <v>46215</v>
       </c>
       <c r="D121">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E121">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F121">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H121">
         <v>119</v>
@@ -4143,29 +4356,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2027-W17</t>
-        </is>
-      </c>
-      <c r="B122" s="2">
-        <v>46503</v>
-      </c>
-      <c r="C122" s="2">
-        <v>46509</v>
+    <row r="122" spans="1:9">
+      <c r="A122" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" s="1">
+        <v>46216</v>
+      </c>
+      <c r="C122" s="1">
+        <v>46222</v>
       </c>
       <c r="D122">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E122">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F122">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H122">
         <v>120</v>
@@ -4174,29 +4385,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2027-W18</t>
-        </is>
-      </c>
-      <c r="B123" s="2">
-        <v>46510</v>
-      </c>
-      <c r="C123" s="2">
-        <v>46516</v>
+    <row r="123" spans="1:9">
+      <c r="A123" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C123" s="1">
+        <v>46229</v>
       </c>
       <c r="D123">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E123">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F123">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H123">
         <v>121</v>
@@ -4205,29 +4414,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2027-W19</t>
-        </is>
-      </c>
-      <c r="B124" s="2">
-        <v>46517</v>
-      </c>
-      <c r="C124" s="2">
-        <v>46523</v>
+    <row r="124" spans="1:9">
+      <c r="A124" t="s">
+        <v>131</v>
+      </c>
+      <c r="B124" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C124" s="1">
+        <v>46236</v>
       </c>
       <c r="D124">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E124">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F124">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H124">
         <v>122</v>
@@ -4236,29 +4443,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2027-W20</t>
-        </is>
-      </c>
-      <c r="B125" s="2">
-        <v>46524</v>
-      </c>
-      <c r="C125" s="2">
-        <v>46530</v>
+    <row r="125" spans="1:9">
+      <c r="A125" t="s">
+        <v>132</v>
+      </c>
+      <c r="B125" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C125" s="1">
+        <v>46243</v>
       </c>
       <c r="D125">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E125">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F125">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G125">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H125">
         <v>123</v>
@@ -4267,29 +4472,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2027-W21</t>
-        </is>
-      </c>
-      <c r="B126" s="2">
-        <v>46531</v>
-      </c>
-      <c r="C126" s="2">
-        <v>46537</v>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>133</v>
+      </c>
+      <c r="B126" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C126" s="1">
+        <v>46250</v>
       </c>
       <c r="D126">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E126">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F126">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G126">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H126">
         <v>124</v>
@@ -4298,29 +4501,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2027-W22</t>
-        </is>
-      </c>
-      <c r="B127" s="2">
-        <v>46538</v>
-      </c>
-      <c r="C127" s="2">
-        <v>46544</v>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" s="1">
+        <v>46251</v>
+      </c>
+      <c r="C127" s="1">
+        <v>46257</v>
       </c>
       <c r="D127">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E127">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F127">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H127">
         <v>125</v>
@@ -4329,29 +4530,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2027-W23</t>
-        </is>
-      </c>
-      <c r="B128" s="2">
-        <v>46545</v>
-      </c>
-      <c r="C128" s="2">
-        <v>46551</v>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>135</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46258</v>
+      </c>
+      <c r="C128" s="1">
+        <v>46264</v>
       </c>
       <c r="D128">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E128">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F128">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G128">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H128">
         <v>126</v>
@@ -4360,29 +4559,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2027-W24</t>
-        </is>
-      </c>
-      <c r="B129" s="2">
-        <v>46552</v>
-      </c>
-      <c r="C129" s="2">
-        <v>46558</v>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
+        <v>136</v>
+      </c>
+      <c r="B129" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C129" s="1">
+        <v>46271</v>
       </c>
       <c r="D129">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E129">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F129">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G129">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H129">
         <v>127</v>
@@ -4391,29 +4588,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2027-W25</t>
-        </is>
-      </c>
-      <c r="B130" s="2">
-        <v>46559</v>
-      </c>
-      <c r="C130" s="2">
-        <v>46565</v>
+    <row r="130" spans="1:9">
+      <c r="A130" t="s">
+        <v>137</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46272</v>
+      </c>
+      <c r="C130" s="1">
+        <v>46278</v>
       </c>
       <c r="D130">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E130">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F130">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H130">
         <v>128</v>
@@ -4422,29 +4617,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2027-W26</t>
-        </is>
-      </c>
-      <c r="B131" s="2">
-        <v>46566</v>
-      </c>
-      <c r="C131" s="2">
-        <v>46572</v>
+    <row r="131" spans="1:9">
+      <c r="A131" t="s">
+        <v>138</v>
+      </c>
+      <c r="B131" s="1">
+        <v>46279</v>
+      </c>
+      <c r="C131" s="1">
+        <v>46285</v>
       </c>
       <c r="D131">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E131">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F131">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H131">
         <v>129</v>
@@ -4453,26 +4646,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2027-W27</t>
-        </is>
-      </c>
-      <c r="B132" s="2">
-        <v>46573</v>
-      </c>
-      <c r="C132" s="2">
-        <v>46579</v>
+    <row r="132" spans="1:9">
+      <c r="A132" t="s">
+        <v>139</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C132" s="1">
+        <v>46292</v>
       </c>
       <c r="D132">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E132">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F132">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G132">
         <v>3</v>
@@ -4484,26 +4675,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2027-W28</t>
-        </is>
-      </c>
-      <c r="B133" s="2">
-        <v>46580</v>
-      </c>
-      <c r="C133" s="2">
-        <v>46586</v>
+    <row r="133" spans="1:9">
+      <c r="A133" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" s="1">
+        <v>46293</v>
+      </c>
+      <c r="C133" s="1">
+        <v>46299</v>
       </c>
       <c r="D133">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E133">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F133">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G133">
         <v>3</v>
@@ -4515,29 +4704,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2027-W29</t>
-        </is>
-      </c>
-      <c r="B134" s="2">
-        <v>46587</v>
-      </c>
-      <c r="C134" s="2">
-        <v>46593</v>
+    <row r="134" spans="1:9">
+      <c r="A134" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" s="1">
+        <v>46300</v>
+      </c>
+      <c r="C134" s="1">
+        <v>46306</v>
       </c>
       <c r="D134">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E134">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F134">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H134">
         <v>132</v>
@@ -4546,29 +4733,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2027-W30</t>
-        </is>
-      </c>
-      <c r="B135" s="2">
-        <v>46594</v>
-      </c>
-      <c r="C135" s="2">
-        <v>46600</v>
+    <row r="135" spans="1:9">
+      <c r="A135" t="s">
+        <v>142</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46307</v>
+      </c>
+      <c r="C135" s="1">
+        <v>46313</v>
       </c>
       <c r="D135">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E135">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F135">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G135">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H135">
         <v>133</v>
@@ -4577,29 +4762,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2027-W31</t>
-        </is>
-      </c>
-      <c r="B136" s="2">
-        <v>46601</v>
-      </c>
-      <c r="C136" s="2">
-        <v>46607</v>
+    <row r="136" spans="1:9">
+      <c r="A136" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C136" s="1">
+        <v>46320</v>
       </c>
       <c r="D136">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E136">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F136">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G136">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H136">
         <v>134</v>
@@ -4608,29 +4791,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2027-W32</t>
-        </is>
-      </c>
-      <c r="B137" s="2">
-        <v>46608</v>
-      </c>
-      <c r="C137" s="2">
-        <v>46614</v>
+    <row r="137" spans="1:9">
+      <c r="A137" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" s="1">
+        <v>46321</v>
+      </c>
+      <c r="C137" s="1">
+        <v>46327</v>
       </c>
       <c r="D137">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E137">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F137">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H137">
         <v>135</v>
@@ -4639,29 +4820,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2027-W33</t>
-        </is>
-      </c>
-      <c r="B138" s="2">
-        <v>46615</v>
-      </c>
-      <c r="C138" s="2">
-        <v>46621</v>
+    <row r="138" spans="1:9">
+      <c r="A138" t="s">
+        <v>145</v>
+      </c>
+      <c r="B138" s="1">
+        <v>46328</v>
+      </c>
+      <c r="C138" s="1">
+        <v>46334</v>
       </c>
       <c r="D138">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E138">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F138">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H138">
         <v>136</v>
@@ -4670,29 +4849,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2027-W34</t>
-        </is>
-      </c>
-      <c r="B139" s="2">
-        <v>46622</v>
-      </c>
-      <c r="C139" s="2">
-        <v>46628</v>
+    <row r="139" spans="1:9">
+      <c r="A139" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" s="1">
+        <v>46335</v>
+      </c>
+      <c r="C139" s="1">
+        <v>46341</v>
       </c>
       <c r="D139">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E139">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F139">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G139">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H139">
         <v>137</v>
@@ -4701,29 +4878,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2027-W35</t>
-        </is>
-      </c>
-      <c r="B140" s="2">
-        <v>46629</v>
-      </c>
-      <c r="C140" s="2">
-        <v>46635</v>
+    <row r="140" spans="1:9">
+      <c r="A140" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46342</v>
+      </c>
+      <c r="C140" s="1">
+        <v>46348</v>
       </c>
       <c r="D140">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E140">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F140">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H140">
         <v>138</v>
@@ -4732,29 +4907,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2027-W36</t>
-        </is>
-      </c>
-      <c r="B141" s="2">
-        <v>46636</v>
-      </c>
-      <c r="C141" s="2">
-        <v>46642</v>
+    <row r="141" spans="1:9">
+      <c r="A141" t="s">
+        <v>148</v>
+      </c>
+      <c r="B141" s="1">
+        <v>46349</v>
+      </c>
+      <c r="C141" s="1">
+        <v>46355</v>
       </c>
       <c r="D141">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E141">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F141">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H141">
         <v>139</v>
@@ -4763,29 +4936,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2027-W37</t>
-        </is>
-      </c>
-      <c r="B142" s="2">
-        <v>46643</v>
-      </c>
-      <c r="C142" s="2">
-        <v>46649</v>
+    <row r="142" spans="1:9">
+      <c r="A142" t="s">
+        <v>149</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46356</v>
+      </c>
+      <c r="C142" s="1">
+        <v>46362</v>
       </c>
       <c r="D142">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E142">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F142">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G142">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H142">
         <v>140</v>
@@ -4794,29 +4965,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2027-W38</t>
-        </is>
-      </c>
-      <c r="B143" s="2">
-        <v>46650</v>
-      </c>
-      <c r="C143" s="2">
-        <v>46656</v>
+    <row r="143" spans="1:9">
+      <c r="A143" t="s">
+        <v>150</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46363</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46369</v>
       </c>
       <c r="D143">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E143">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F143">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G143">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H143">
         <v>141</v>
@@ -4825,29 +4994,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2027-W39</t>
-        </is>
-      </c>
-      <c r="B144" s="2">
-        <v>46657</v>
-      </c>
-      <c r="C144" s="2">
-        <v>46663</v>
+    <row r="144" spans="1:9">
+      <c r="A144" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" s="1">
+        <v>46370</v>
+      </c>
+      <c r="C144" s="1">
+        <v>46376</v>
       </c>
       <c r="D144">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E144">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F144">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G144">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H144">
         <v>142</v>
@@ -4856,26 +5023,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2027-W40</t>
-        </is>
-      </c>
-      <c r="B145" s="2">
-        <v>46664</v>
-      </c>
-      <c r="C145" s="2">
-        <v>46670</v>
+    <row r="145" spans="1:9">
+      <c r="A145" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46377</v>
+      </c>
+      <c r="C145" s="1">
+        <v>46383</v>
       </c>
       <c r="D145">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E145">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F145">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G145">
         <v>4</v>
@@ -4887,26 +5052,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2027-W41</t>
-        </is>
-      </c>
-      <c r="B146" s="2">
-        <v>46671</v>
-      </c>
-      <c r="C146" s="2">
-        <v>46677</v>
+    <row r="146" spans="1:9">
+      <c r="A146" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" s="1">
+        <v>46384</v>
+      </c>
+      <c r="C146" s="1">
+        <v>46390</v>
       </c>
       <c r="D146">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E146">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F146">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G146">
         <v>4</v>
@@ -4918,29 +5081,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2027-W42</t>
-        </is>
-      </c>
-      <c r="B147" s="2">
-        <v>46678</v>
-      </c>
-      <c r="C147" s="2">
-        <v>46684</v>
+    <row r="147" spans="1:9">
+      <c r="A147" t="s">
+        <v>154</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46391</v>
+      </c>
+      <c r="C147" s="1">
+        <v>46397</v>
       </c>
       <c r="D147">
         <v>2027</v>
       </c>
       <c r="E147">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F147">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G147">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H147">
         <v>145</v>
@@ -4949,29 +5110,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2027-W43</t>
-        </is>
-      </c>
-      <c r="B148" s="2">
-        <v>46685</v>
-      </c>
-      <c r="C148" s="2">
-        <v>46691</v>
+    <row r="148" spans="1:9">
+      <c r="A148" t="s">
+        <v>155</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46398</v>
+      </c>
+      <c r="C148" s="1">
+        <v>46404</v>
       </c>
       <c r="D148">
         <v>2027</v>
       </c>
       <c r="E148">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="F148">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G148">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H148">
         <v>146</v>
@@ -4980,29 +5139,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2027-W44</t>
-        </is>
-      </c>
-      <c r="B149" s="2">
-        <v>46692</v>
-      </c>
-      <c r="C149" s="2">
-        <v>46698</v>
+    <row r="149" spans="1:9">
+      <c r="A149" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46405</v>
+      </c>
+      <c r="C149" s="1">
+        <v>46411</v>
       </c>
       <c r="D149">
         <v>2027</v>
       </c>
       <c r="E149">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="F149">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G149">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H149">
         <v>147</v>
@@ -5011,29 +5168,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2027-W45</t>
-        </is>
-      </c>
-      <c r="B150" s="2">
-        <v>46699</v>
-      </c>
-      <c r="C150" s="2">
-        <v>46705</v>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" s="1">
+        <v>46412</v>
+      </c>
+      <c r="C150" s="1">
+        <v>46418</v>
       </c>
       <c r="D150">
         <v>2027</v>
       </c>
       <c r="E150">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F150">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G150">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H150">
         <v>148</v>
@@ -5042,29 +5197,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2027-W46</t>
-        </is>
-      </c>
-      <c r="B151" s="2">
-        <v>46706</v>
-      </c>
-      <c r="C151" s="2">
-        <v>46712</v>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46419</v>
+      </c>
+      <c r="C151" s="1">
+        <v>46425</v>
       </c>
       <c r="D151">
         <v>2027</v>
       </c>
       <c r="E151">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="F151">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G151">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H151">
         <v>149</v>
@@ -5073,29 +5226,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2027-W47</t>
-        </is>
-      </c>
-      <c r="B152" s="2">
-        <v>46713</v>
-      </c>
-      <c r="C152" s="2">
-        <v>46719</v>
+    <row r="152" spans="1:9">
+      <c r="A152" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" s="1">
+        <v>46426</v>
+      </c>
+      <c r="C152" s="1">
+        <v>46432</v>
       </c>
       <c r="D152">
         <v>2027</v>
       </c>
       <c r="E152">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F152">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G152">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H152">
         <v>150</v>
@@ -5104,29 +5255,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2027-W48</t>
-        </is>
-      </c>
-      <c r="B153" s="2">
-        <v>46720</v>
-      </c>
-      <c r="C153" s="2">
-        <v>46726</v>
+    <row r="153" spans="1:9">
+      <c r="A153" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" s="1">
+        <v>46433</v>
+      </c>
+      <c r="C153" s="1">
+        <v>46439</v>
       </c>
       <c r="D153">
         <v>2027</v>
       </c>
       <c r="E153">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="F153">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G153">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H153">
         <v>151</v>
@@ -5135,29 +5284,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2027-W49</t>
-        </is>
-      </c>
-      <c r="B154" s="2">
-        <v>46727</v>
-      </c>
-      <c r="C154" s="2">
-        <v>46733</v>
+    <row r="154" spans="1:9">
+      <c r="A154" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46440</v>
+      </c>
+      <c r="C154" s="1">
+        <v>46446</v>
       </c>
       <c r="D154">
         <v>2027</v>
       </c>
       <c r="E154">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="F154">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G154">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H154">
         <v>152</v>
@@ -5166,29 +5313,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2027-W50</t>
-        </is>
-      </c>
-      <c r="B155" s="2">
-        <v>46734</v>
-      </c>
-      <c r="C155" s="2">
-        <v>46740</v>
+    <row r="155" spans="1:9">
+      <c r="A155" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" s="1">
+        <v>46447</v>
+      </c>
+      <c r="C155" s="1">
+        <v>46453</v>
       </c>
       <c r="D155">
         <v>2027</v>
       </c>
       <c r="E155">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F155">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G155">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H155">
         <v>153</v>
@@ -5197,29 +5342,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2027-W51</t>
-        </is>
-      </c>
-      <c r="B156" s="2">
-        <v>46741</v>
-      </c>
-      <c r="C156" s="2">
-        <v>46747</v>
+    <row r="156" spans="1:9">
+      <c r="A156" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" s="1">
+        <v>46454</v>
+      </c>
+      <c r="C156" s="1">
+        <v>46460</v>
       </c>
       <c r="D156">
         <v>2027</v>
       </c>
       <c r="E156">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F156">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G156">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H156">
         <v>154</v>
@@ -5228,29 +5371,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2027-W52</t>
-        </is>
-      </c>
-      <c r="B157" s="2">
-        <v>46748</v>
-      </c>
-      <c r="C157" s="2">
-        <v>46754</v>
+    <row r="157" spans="1:9">
+      <c r="A157" t="s">
+        <v>164</v>
+      </c>
+      <c r="B157" s="1">
+        <v>46461</v>
+      </c>
+      <c r="C157" s="1">
+        <v>46467</v>
       </c>
       <c r="D157">
         <v>2027</v>
       </c>
       <c r="E157">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F157">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G157">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H157">
         <v>155</v>
@@ -5260,7 +5401,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I157"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>